--- a/erp-server/erp-server-file/src/main/resources/excel/oms/kolSocialMediaExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/kolSocialMediaExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24945" windowHeight="17655"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="回片列表" sheetId="4" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>类型</t>
   </si>
@@ -774,14 +774,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1112,7 +1109,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
@@ -1125,10 +1122,10 @@
     <col min="11" max="11" width="17.875" customWidth="1"/>
     <col min="12" max="12" width="16.625" customWidth="1"/>
     <col min="13" max="13" width="14.25" customWidth="1"/>
-    <col min="14" max="17" width="12.125" customWidth="1"/>
+    <col min="14" max="16" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1138,50 +1135,47 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
@@ -1191,47 +1185,44 @@
       <c r="C2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/kolSocialMediaExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/kolSocialMediaExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="24945" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="回片列表" sheetId="4" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>类型</t>
   </si>
@@ -774,11 +774,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1109,7 +1112,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
@@ -1122,10 +1125,10 @@
     <col min="11" max="11" width="17.875" customWidth="1"/>
     <col min="12" max="12" width="16.625" customWidth="1"/>
     <col min="13" max="13" width="14.25" customWidth="1"/>
-    <col min="14" max="16" width="12.125" customWidth="1"/>
+    <col min="14" max="17" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1135,47 +1138,50 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
@@ -1185,44 +1191,47 @@
       <c r="C2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>31</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
